--- a/用车费用明细.xlsx
+++ b/用车费用明细.xlsx
@@ -1787,6 +1787,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1812,6 +1815,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1837,6 +1843,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1862,6 +1871,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1887,6 +1899,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1912,6 +1927,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1937,6 +1955,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1962,6 +1983,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1987,6 +2011,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2012,6 +2039,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2037,6 +2067,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2062,6 +2095,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2087,6 +2123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2112,6 +2151,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2137,6 +2179,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2162,6 +2207,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2187,6 +2235,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2212,6 +2263,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2237,6 +2291,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2262,6 +2319,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2281,6 +2341,534 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>

--- a/用车费用明细.xlsx
+++ b/用车费用明细.xlsx
@@ -2375,6 +2375,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2400,6 +2403,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2425,6 +2431,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2450,6 +2459,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2475,6 +2487,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2500,6 +2515,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2525,6 +2543,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2550,6 +2571,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2575,6 +2599,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2600,6 +2627,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2625,6 +2655,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2650,6 +2683,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2675,6 +2711,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2700,6 +2739,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2725,6 +2767,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2750,6 +2795,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2775,6 +2823,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2800,6 +2851,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2825,6 +2879,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2850,6 +2907,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2869,6 +2929,534 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1543050" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3324,7 +3912,9 @@
         <v/>
       </c>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
+      <c r="K5" s="4" t="n">
+        <v>86</v>
+      </c>
       <c r="L5" s="3" t="n"/>
     </row>
     <row r="6" ht="37" customHeight="1" s="42">
@@ -3358,7 +3948,9 @@
         <v/>
       </c>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>76</v>
+      </c>
       <c r="L6" s="3" t="n"/>
     </row>
     <row r="7" ht="37" customHeight="1" s="42">
@@ -3392,7 +3984,9 @@
         <v/>
       </c>
       <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="3" t="n"/>
     </row>
     <row r="8" ht="37" customHeight="1" s="42">
@@ -3426,7 +4020,9 @@
         <v/>
       </c>
       <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="3" t="n"/>
     </row>
     <row r="9" ht="37" customHeight="1" s="42">
@@ -3460,7 +4056,9 @@
         <v/>
       </c>
       <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="3" t="n"/>
     </row>
     <row r="10" ht="37" customHeight="1" s="42">
@@ -3494,7 +4092,9 @@
         <v/>
       </c>
       <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="3" t="n"/>
     </row>
     <row r="11" ht="37" customHeight="1" s="42">
@@ -3528,7 +4128,9 @@
         <v/>
       </c>
       <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="3" t="n"/>
     </row>
     <row r="12" ht="37" customHeight="1" s="42">
@@ -3562,7 +4164,9 @@
         <v/>
       </c>
       <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="3" t="n"/>
     </row>
     <row r="13" ht="37" customHeight="1" s="42">
@@ -3596,7 +4200,9 @@
         <v/>
       </c>
       <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
+      <c r="K13" s="4" t="n">
+        <v>80.75</v>
+      </c>
       <c r="L13" s="3" t="n"/>
     </row>
     <row r="14" ht="37" customHeight="1" s="42">
@@ -3630,7 +4236,9 @@
         <v/>
       </c>
       <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
+      <c r="K14" s="4" t="n">
+        <v>73.15000000000001</v>
+      </c>
       <c r="L14" s="3" t="n"/>
     </row>
     <row r="15" ht="37" customHeight="1" s="42">
@@ -3664,7 +4272,9 @@
         <v/>
       </c>
       <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="K15" s="4" t="n">
+        <v>73.15000000000001</v>
+      </c>
       <c r="L15" s="3" t="n"/>
     </row>
     <row r="16" ht="37" customHeight="1" s="42">
@@ -3698,7 +4308,9 @@
         <v/>
       </c>
       <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="K16" s="4" t="n">
+        <v>71.25</v>
+      </c>
       <c r="L16" s="3" t="n"/>
     </row>
     <row r="17" ht="37" customHeight="1" s="42">
@@ -3732,7 +4344,9 @@
         <v/>
       </c>
       <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="K17" s="4" t="n">
+        <v>63.65</v>
+      </c>
       <c r="L17" s="3" t="n"/>
     </row>
     <row r="18" ht="39" customHeight="1" s="42">
@@ -3766,7 +4380,9 @@
         <v/>
       </c>
       <c r="J18" s="24" t="n"/>
-      <c r="K18" s="24" t="n"/>
+      <c r="K18" s="24" t="n">
+        <v>63.65</v>
+      </c>
       <c r="L18" s="25" t="n"/>
     </row>
     <row r="19" ht="29" customHeight="1" s="42">
@@ -3800,7 +4416,9 @@
         <v/>
       </c>
       <c r="J19" s="24" t="n"/>
-      <c r="K19" s="24" t="n"/>
+      <c r="K19" s="24" t="n">
+        <v>73.15000000000001</v>
+      </c>
       <c r="L19" s="25" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1" s="42">
@@ -3834,7 +4452,9 @@
         <v/>
       </c>
       <c r="J20" s="24" t="n"/>
-      <c r="K20" s="24" t="n"/>
+      <c r="K20" s="24" t="n">
+        <v>76.5</v>
+      </c>
       <c r="L20" s="25" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1" s="42">

--- a/用车费用明细.xlsx
+++ b/用车费用明细.xlsx
@@ -558,2405 +558,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1543050" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2977,11 +583,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3002,11 +608,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3027,11 +633,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3052,11 +658,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3077,11 +683,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3102,11 +708,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3127,11 +733,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3152,11 +758,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3177,11 +783,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3202,11 +808,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3227,11 +833,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3252,11 +858,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3277,11 +883,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3302,11 +908,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3327,11 +933,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3352,11 +958,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3377,11 +983,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3402,11 +1008,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3427,11 +1033,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3452,11 +1058,11 @@
     <ext cx="1543050" cy="2057400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3787,7 +1393,7 @@
       <c r="H2" s="35" t="n"/>
       <c r="I2" s="43" t="inlineStr">
         <is>
-          <t>制表日期：2026年5月28日</t>
+          <t>制表日期：2026年5月30日</t>
         </is>
       </c>
       <c r="J2" s="34" t="n"/>
@@ -4581,20 +2187,7 @@
       <c r="K25" s="12" t="n"/>
       <c r="L25" s="12" t="n"/>
     </row>
-    <row r="26" ht="170" customHeight="1" s="42">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-    </row>
+    <row r="26" ht="170" customHeight="1" s="42"/>
     <row r="27" ht="25" customHeight="1" s="42">
       <c r="B27" s="45" t="inlineStr">
         <is>
@@ -4642,7 +2235,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F28" s="49" t="inlineStr">
+      <c r="F28" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4666,7 +2259,7 @@
           <t>合肥市·云谷创新园</t>
         </is>
       </c>
-      <c r="F29" s="49" t="inlineStr">
+      <c r="F29" s="48" t="inlineStr">
         <is>
           <t>北纬 31°42', 东经 117°16'</t>
         </is>
@@ -4690,7 +2283,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F30" s="49" t="inlineStr">
+      <c r="F30" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4714,7 +2307,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F31" s="49" t="inlineStr">
+      <c r="F31" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4738,7 +2331,7 @@
           <t>马鞍山市·安徽天邦生物技术有限公司</t>
         </is>
       </c>
-      <c r="F32" s="49" t="inlineStr">
+      <c r="F32" s="48" t="inlineStr">
         <is>
           <t>北纬 31°40', 东经 118°27'</t>
         </is>
@@ -4762,7 +2355,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F33" s="49" t="inlineStr">
+      <c r="F33" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4786,7 +2379,7 @@
           <t>马鞍山市·安徽天邦生物技术有限公司</t>
         </is>
       </c>
-      <c r="F34" s="49" t="inlineStr">
+      <c r="F34" s="48" t="inlineStr">
         <is>
           <t>北纬 31°40', 东经 118°27'</t>
         </is>
@@ -4810,7 +2403,7 @@
           <t>南京市·南京市六合区信访局</t>
         </is>
       </c>
-      <c r="F35" s="49" t="inlineStr">
+      <c r="F35" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4834,7 +2427,7 @@
           <t>马鞍山市·安徽天邦生物技术有限公司</t>
         </is>
       </c>
-      <c r="F36" s="49" t="inlineStr">
+      <c r="F36" s="48" t="inlineStr">
         <is>
           <t>北纬 31°40', 东经 118°27'</t>
         </is>
@@ -4858,7 +2451,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F37" s="49" t="inlineStr">
+      <c r="F37" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4882,7 +2475,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F38" s="49" t="inlineStr">
+      <c r="F38" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4906,7 +2499,7 @@
           <t>合肥市·联投v中心</t>
         </is>
       </c>
-      <c r="F39" s="49" t="inlineStr">
+      <c r="F39" s="48" t="inlineStr">
         <is>
           <t>北纬 31°42', 东经 117°18'</t>
         </is>
@@ -4930,7 +2523,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F40" s="49" t="inlineStr">
+      <c r="F40" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4954,7 +2547,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F41" s="49" t="inlineStr">
+      <c r="F41" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -4978,7 +2571,7 @@
           <t>合肥市·联投v中心</t>
         </is>
       </c>
-      <c r="F42" s="49" t="inlineStr">
+      <c r="F42" s="48" t="inlineStr">
         <is>
           <t>北纬 31°42', 东经 117°18'</t>
         </is>
@@ -5002,7 +2595,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F43" s="49" t="inlineStr">
+      <c r="F43" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -5026,7 +2619,7 @@
           <t>合肥市·联投v中心</t>
         </is>
       </c>
-      <c r="F44" s="49" t="inlineStr">
+      <c r="F44" s="48" t="inlineStr">
         <is>
           <t>北纬 31°42', 东经 117°18'</t>
         </is>
@@ -5050,7 +2643,7 @@
           <t>南京市·璟湖广场</t>
         </is>
       </c>
-      <c r="F45" s="49" t="inlineStr">
+      <c r="F45" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
@@ -5074,7 +2667,7 @@
           <t>南京市·江北新区景枫乐创中心B1栋</t>
         </is>
       </c>
-      <c r="F46" s="49" t="inlineStr">
+      <c r="F46" s="48" t="inlineStr">
         <is>
           <t>北纬 32°02', 东经 118°38'</t>
         </is>
@@ -5098,7 +2691,7 @@
           <t>合肥市·联投v中心</t>
         </is>
       </c>
-      <c r="F47" s="49" t="inlineStr">
+      <c r="F47" s="48" t="inlineStr">
         <is>
           <t>北纬 31°42', 东经 117°18'</t>
         </is>
@@ -5122,7 +2715,7 @@
           <t>南京市·龙池翠洲</t>
         </is>
       </c>
-      <c r="F48" s="49" t="inlineStr">
+      <c r="F48" s="48" t="inlineStr">
         <is>
           <t>北纬 32°19', 东经 118°49'</t>
         </is>
